--- a/resources/(언진) 수집 제외 도메인 주소_공식 블로그.xlsx
+++ b/resources/(언진) 수집 제외 도메인 주소_공식 블로그.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GM\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\원일남\일일업무보고\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DB0F876-8919-4227-B532-075491D4F1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{59924752-7591-4319-8475-07810F4B5641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$254</definedName>
     <definedName name="POWER_USER_LINK_020942E5_A6D8_46D2_8474_A22983F60BD0" comment="{&quot;Id&quot;:&quot;POWER_USER_LINK_020942E5_A6D8_46D2_8474_A22983F60BD0&quot;,&quot;SourceFullName&quot;:&quot;C:\\Users\\GM\\Desktop\\(매체)모니터링 전체 데이터.xlsx!Sheet2!R13C11:R15C13&quot;,&quot;LastUpdate&quot;:&quot;2024-10-02 2:20 PM&quot;,&quot;UpdatedBy&quot;:&quot;GM&quot;,&quot;IsLinked&quot;:true,&quot;IsBrokenLink&quot;:false,&quot;Type&quot;:2}">#REF!</definedName>
     <definedName name="POWER_USER_LINK_1390EFAC_3122_47A5_9670_644BE94ABD50" comment="{&quot;Id&quot;:&quot;POWER_USER_LINK_1390EFAC_3122_47A5_9670_644BE94ABD50&quot;,&quot;SourceFullName&quot;:&quot;C:\\Users\\GM\\Desktop\\(매체)모니터링 전체 데이터.xlsx!Sheet1!POWER_USER_LINK_C5B0219C_97AA_4737_A6E6_FA6CAC0B715C&quot;,&quot;LastUpdate&quot;:&quot;2024-10-02 1:16 PM&quot;,&quot;UpdatedBy&quot;:&quot;GM&quot;,&quot;IsLinked&quot;:true,&quot;Is">#REF!</definedName>
     <definedName name="POWER_USER_LINK_4A602CFC_AE66_4967_9AB4_F72EDB16084C" comment="{&quot;Id&quot;:&quot;POWER_USER_LINK_4A602CFC_AE66_4967_9AB4_F72EDB16084C&quot;,&quot;SourceFullName&quot;:&quot;C:\\Users\\GM\\Desktop\\(매체)모니터링 전체 데이터.xlsx!Sheet2!R5C8:R7C14&quot;,&quot;LastUpdate&quot;:&quot;2024-10-04 3:22 PM&quot;,&quot;UpdatedBy&quot;:&quot;GM&quot;,&quot;IsLinked&quot;:true,&quot;IsBrokenLink&quot;:false,&quot;Type&quot;:2}">#REF!</definedName>
@@ -28,73 +29,28 @@
     <definedName name="POWER_USER_LINK_DBD778E4_E895_4833_BA78_D4E361747380" comment="{&quot;Id&quot;:&quot;POWER_USER_LINK_DBD778E4_E895_4833_BA78_D4E361747380&quot;,&quot;SourceFullName&quot;:&quot;C:\\Users\\GM\\Desktop\\(매체)모니터링 전체 데이터.xlsx!Sheet1!R6C11:R8C17&quot;,&quot;LastUpdate&quot;:&quot;2024-10-02 11:23 AM&quot;,&quot;UpdatedBy&quot;:&quot;GM&quot;,&quot;IsLinked&quot;:true,&quot;IsBrokenLink&quot;:false,&quot;Type&quot;:2}">#REF!</definedName>
     <definedName name="POWER_USER_LINK_DE512BB8_F5E2_4EA7_9E33_B9AA28C86983" comment="{&quot;Id&quot;:&quot;POWER_USER_LINK_DE512BB8_F5E2_4EA7_9E33_B9AA28C86983&quot;,&quot;SourceFullName&quot;:&quot;C:\\Users\\GM\\Desktop\\(매체)모니터링 전체 데이터.xlsx!Sheet1!POWER_USER_LINK_C5B0219C_97AA_4737_A6E6_FA6CAC0B715C&quot;,&quot;LastUpdate&quot;:&quot;2024-10-02 11:33 AM&quot;,&quot;UpdatedBy&quot;:&quot;GM&quot;,&quot;IsLinked&quot;:true,&quot;I">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="254">
   <si>
     <t>제외 도메인 주소(블로그)</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>https://blog.naver.com/et_news</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://blog.naver.com/brnews0915</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://blog.naver.com/mark0804</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://blog.naver.com/halla-ilbo</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://blog.naver.com/huhykook</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://blog.naver.com/saam0615</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://blog.naver.com/joongbooilbo</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://blog.naver.com/newsmetro</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://blog.naver.com/vipgim1390</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://blog.naver.com/beaureater</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://blog.naver.com/lee_kwang_jae</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://blog.naver.com/jtkim4011</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://blog.naver.com/kangwonilbo</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://blog.naver.com/PostList.naver?blogId=o_jh2056</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>https://blog.naver.com/PostView.naver?blogId=vipgim1390</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -108,6 +64,754 @@
   </si>
   <si>
     <t>https://blog.naver.com/PostView.naver?blogId=lch987600</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=swnewspaper</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ctn_cheonan_new</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=k041036</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=2013jjctv</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=newsb21</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=jsymca</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=peoplegate1</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=phenomdark</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=eunsh929</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=lee7571486</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=bobjuhouse</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=thys5477</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=libido01</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ktxcks</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=kenoop</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=agpeople</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=cjy9099</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=unbuilding</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=contentsm</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=weekly-cnb</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ksdbs77</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=news33net</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=byki70</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=mc355</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=gjreport</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=elel095</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=wisdot_official</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=iandfox</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ph001144</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=cheumad</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=clmedia_news</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=pressman0520</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=news500</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=sideview2018</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=enhanok70</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=philo515</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=youngkyos</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=danwool</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=jungam-ironware</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=inu958</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=econmedia</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=speconomy</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ecolives</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=chi8776</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=newsbusancom</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=paxmedicalnews</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=lkhan1814</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=tenantnews</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=smailesnail</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=youthhopefoundation</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=pmj7776</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=3rdangle</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=kys3623</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=zaksimlibrary</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=newsonmedi</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=newstopten</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ngojournal</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=dirams</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ilsaeng2</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=youngjin6690</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=newsmeter</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=kkmnews1</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=olchiolchi</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=kdnews21</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=wangbee-</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=worldcities</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=jch4512</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=collabonews</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=thankslee57</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=thespikenews</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=kgolfnews1873</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ngnkjustice</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=kimfilm</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=fashon1</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=yagodm</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=grace1ch</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=joynews24trends</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=chamchiz</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=taenafit</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=thenew2021_</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=choicecys</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ewha_media</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=hsig7</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ivisupport</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=withinenter</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=handicapinews</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=gfnews365</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=beak1616</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=2014ksy</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=news321</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=najjongi2</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=updownnews21</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=wtngo</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=jw4932</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=hcnurseacademy</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=sforum</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=aipostkoreayhd</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=sdakuc</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=th_media</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=yongsanland</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=nh-jeju</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ds2qgd</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ju0047</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=sskim2314</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=esgin_net</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ebiznews1</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ktheum</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=jejunews1</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=waterjournal</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=gksk1010619</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=molegin</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=dongdongssi-</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=jsreturn</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=011shinho</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=efnews</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=jnews019</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=kimnkimmarketing</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ever--green</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=kohj007</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=sky3artt</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=iknowiknow</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=satleceo</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=mrqu</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=jesusjesus486</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=aulerbrian</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=molab_suda</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=kjk200</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=zenitechd</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=koreareg</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=issueon_blog</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=hongjs6</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=hkc0929</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=pulmuonefnc</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=poohpoooh</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=iamjieunpark</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=juanmedia1731</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=tone123</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=flyhong21</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=20min_830</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=tlogistic</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=s6320898</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=gocarnet</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=motormg</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=autodiary1</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=soop_kr</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=jmustang</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=rubronegro</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=racer_r1</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ysc14</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=gyment</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=autocarkor</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ibisall</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=vty4989</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=yhc114</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=jae12yam</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=dwyun60</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=jongrodkkim</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=knudh0601</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=binggresmile</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=namdojournal2020</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=jinhakscience</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=sjjeon001</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ynyhnews</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=simml</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=kjw9648</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=pcnorkr</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ljem0809</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=9188lsh</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=jejuec2012</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=namwonsinmun</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=prpepper11</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=vulbai</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=kormadangnews</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=kjtimes1</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=springmen</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=nsmiso</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=law1800</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=igasjournal</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=dms1455</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=co2korea</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=jinrocals</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=nohssy</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=iamewp</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=tamsaj</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=yyjjss3081</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=kwtimes</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=cartvnews</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=pan0077</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=gunbo-blog</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=m904</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=o_jh2056</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=scnambh1</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=jbkjbk2002</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=parkty22</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=tkdaily</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=gst3000</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=kmaeil1989</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=g-tvnews</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ghchoi666</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=techkibo</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ksg2028</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=jwkim2916</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=jesus53-</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=4179ts</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=chuny98</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=online-news</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=klan9800</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=kfoenews</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=animalkawa</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=golftimes17</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ch6116ch</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=echo_hkbs</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=06rnftkrrl</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=smu_official</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=segyecom</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=kmts9</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=sisa2022</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=mino0401</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=silverekn</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=asandailynew</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=anyang_naeil</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=keeisns</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=asiainews</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=mnews_</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=councilulsan</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=p8725</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=powerkorea0505</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=youcandonews</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=kbcd2008</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=withinnews</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=yjw8817</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=63swlee</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=infostock2018</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=jb11101</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=jbfocus__</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=cskcr</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ccdailynews</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=thecm11</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=vanilla1003</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=tkpress82</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ptmnews</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=seo8587</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=ceo009</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=texnews</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=koreadisablednews</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=korearailroadnews</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=cmcsong</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=honamnews24</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/PostView.naver?blogId=jnamdonews</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -209,13 +913,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
@@ -528,7 +1235,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:P90"/>
+  <dimension ref="A1:P254"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.875" customWidth="1"/>
@@ -562,98 +1269,1258 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="16:16" x14ac:dyDescent="0.3">
-      <c r="P90" s="1"/>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>74</v>
+      </c>
+      <c r="P76" s="1"/>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A195" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A196" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A197" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A198" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A199" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A200" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A201" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A202" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A203" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A204" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A205" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A206" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A207" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A208" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A209" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A210" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A211" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A212" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A213" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A214" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A215" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A216" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A217" s="4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A218" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A219" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A220" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A221" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A222" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A223" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A224" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A225" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A226" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A227" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A228" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A229" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A230" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A231" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A232" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A233" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A234" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A235" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A236" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A237" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A238" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A239" s="4" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A240" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A241" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A242" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A243" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A244" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A245" s="4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A246" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A247" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A248" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A249" s="4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A250" s="4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A251" s="4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A252" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A253" s="4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A254" s="4" t="s">
+        <v>252</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{795B6E95-F482-4D7F-9BE8-18A194170F23}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{7756DCF6-8A60-4AFE-8D9D-3EB1E1462518}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{D94879E0-7E44-4CE5-8C7D-C0F8B3AF7E06}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{F537E30D-A273-441D-870B-4D0544A4D574}"/>
-    <hyperlink ref="A6" r:id="rId5" xr:uid="{F7C6C8BF-8205-4F4F-BD0B-1A40F7535BB5}"/>
-    <hyperlink ref="A7" r:id="rId6" xr:uid="{FE90DEBF-C978-4184-8381-1D8CAF041EC0}"/>
-    <hyperlink ref="A8" r:id="rId7" xr:uid="{5E465B07-E7D4-4D0B-A9C3-DCB3A2F625C9}"/>
-    <hyperlink ref="A9" r:id="rId8" xr:uid="{40E70662-E84A-4164-8D05-E942C94EAEC7}"/>
-    <hyperlink ref="A10" r:id="rId9" xr:uid="{4794FDD0-4482-4481-AFF6-4028C72976BE}"/>
-    <hyperlink ref="A11" r:id="rId10" xr:uid="{B0204E00-46C5-41DD-B920-6D73446F6689}"/>
-    <hyperlink ref="A12" r:id="rId11" xr:uid="{B76BF7A1-593B-4C38-98F9-DD95F3655352}"/>
-    <hyperlink ref="A13" r:id="rId12" xr:uid="{52564797-6ADA-4713-88A8-850314534947}"/>
-    <hyperlink ref="A14" r:id="rId13" xr:uid="{E1A7A5D9-6FF2-4FCF-AD91-962E1AD9651F}"/>
-    <hyperlink ref="A15" r:id="rId14" xr:uid="{A52910B2-4EC8-4329-AC0F-CB4E8306DA66}"/>
-    <hyperlink ref="A16" r:id="rId15" xr:uid="{7579959D-C9C1-437D-8BB8-EAAFAEEE791F}"/>
-    <hyperlink ref="A17" r:id="rId16" xr:uid="{3F9E6972-EBBB-4E89-875E-7DA6A6386508}"/>
-    <hyperlink ref="A18" r:id="rId17" xr:uid="{D006DE8A-1700-4066-8393-3C44C3FC8390}"/>
-    <hyperlink ref="A19" r:id="rId18" xr:uid="{3273A107-B9C7-4C12-988E-852FD8BA110F}"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{7579959D-C9C1-437D-8BB8-EAAFAEEE791F}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{3F9E6972-EBBB-4E89-875E-7DA6A6386508}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{D006DE8A-1700-4066-8393-3C44C3FC8390}"/>
+    <hyperlink ref="A5" r:id="rId4" xr:uid="{3273A107-B9C7-4C12-988E-852FD8BA110F}"/>
+    <hyperlink ref="A6" r:id="rId5" xr:uid="{56C20E19-8241-4EBD-82EB-F4BC453FB6B0}"/>
   </hyperlinks>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
